--- a/sueños.xlsx
+++ b/sueños.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t xml:space="preserve">* Con Malen discutimos antes de que entrara otra vez en ageac (el ritual de iniciacion)</t>
   </si>
@@ -149,6 +149,12 @@
   </si>
   <si>
     <t xml:space="preserve">Mas tarde en un edificio hubo un TEREMOTO y bese a luz?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kkk dando conferencia y al final se abraza con sus padres internos, despues me canta: EL desencuentro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bernardo se muere?  Voy en el auto con papa escuchando who do you love now  y hago cosas astrales,. Tengo que comprar algo para justificar 3000 de un emprendimiento con gali, anita perez es la contadora para jus</t>
   </si>
 </sst>
 </file>
@@ -253,37 +259,45 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -540,7 +554,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -799,13 +813,29 @@
       <c r="A33" s="8" t="n">
         <v>45933</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="9" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="9" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="10" t="n">
+        <v>-501918</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/sueños.xlsx
+++ b/sueños.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
   <si>
     <t xml:space="preserve">* Con Malen discutimos antes de que entrara otra vez en ageac (el ritual de iniciacion)</t>
   </si>
@@ -155,6 +155,12 @@
   </si>
   <si>
     <t xml:space="preserve">Bernardo se muere?  Voy en el auto con papa escuchando who do you love now  y hago cosas astrales,. Tengo que comprar algo para justificar 3000 de un emprendimiento con gali, anita perez es la contadora para jus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">me cobraron una multa por no llevar la luz de la moto prendida, de 5 millones de pesos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ibamos a festejar que nos casabamos con Malen, en el auto en la puerta de SanMartin, sali a dar la vuelta de manzana porque no me convencio el estacionamiento,  no encontraba donde doblar tuve que ir hasta av.del trabajador, doble a la derecha y subi un monticulo grande, termine en una playa (a 4/8 cuadras de san martin) que se llamaba 25 de noviembre, con lola la perra de los guzman, yo queria volver a 3 arroyos</t>
   </si>
 </sst>
 </file>
@@ -259,7 +265,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -297,10 +303,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -554,7 +556,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -823,19 +825,29 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10" t="n">
+      <c r="A35" s="8" t="n">
         <v>45943</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="9" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10" t="n">
+      <c r="A36" s="8" t="n">
         <v>-501918</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="9" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="0" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/sueños.xlsx
+++ b/sueños.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
   <si>
     <t xml:space="preserve">* Con Malen discutimos antes de que entrara otra vez en ageac (el ritual de iniciacion)</t>
   </si>
@@ -124,7 +124,7 @@
 Por otro lado, vuelvo a soñar que mi madre esta muy mal, la discriminan, llora</t>
   </si>
   <si>
-    <t xml:space="preserve">x lenadro kain</t>
+    <t xml:space="preserve">x leandro kain</t>
   </si>
   <si>
     <t xml:space="preserve">mar 20/may 25</t>
@@ -161,6 +161,15 @@
   </si>
   <si>
     <t xml:space="preserve">Ibamos a festejar que nos casabamos con Malen, en el auto en la puerta de SanMartin, sali a dar la vuelta de manzana porque no me convencio el estacionamiento,  no encontraba donde doblar tuve que ir hasta av.del trabajador, doble a la derecha y subi un monticulo grande, termine en una playa (a 4/8 cuadras de san martin) que se llamaba 25 de noviembre, con lola la perra de los guzman, yo queria volver a 3 arroyos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luz era ciclope, nos pusimos de novio, yo en realidad no queria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabra me acecha, yo puedo saltar la tranquera/alambrado,  creo que esta jja, sobre vuela unh bhuo/lechuza entiendo que es ambos son el ser, me quiere topar, decido no saltar la tranquera, y “estoico” me dejo topar, y era mi ser no mas. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">x fiesta con genteextraña en diag 74</t>
   </si>
 </sst>
 </file>
@@ -204,7 +213,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -213,14 +222,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8CB"/>
-        <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1C4E9"/>
-        <bgColor rgb="FFC0C0C0"/>
+        <fgColor rgb="FF999999"/>
+        <bgColor rgb="FF808080"/>
       </patternFill>
     </fill>
   </fills>
@@ -265,8 +268,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -274,7 +281,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -286,23 +293,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -340,7 +335,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD1C4E9"/>
+      <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -351,7 +346,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFDDE8CB"/>
+      <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -364,7 +359,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -556,164 +551,167 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="12.63"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="n">
+      <c r="A1" s="2" t="n">
         <v>45502</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="5" t="n">
         <v>45505</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>45506</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>45513</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>45525</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>45527</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>45535</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="5" t="n">
         <v>45541</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>45576</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45585</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45609</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3"/>
-      <c r="B17" s="2" t="s">
+      <c r="A17" s="4"/>
+      <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45620</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="5" t="n">
         <v>45631</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="5" t="n">
         <v>45634</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -721,23 +719,23 @@
       <c r="A21" s="5" t="n">
         <v>45660</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="2" t="n">
         <v>45668</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="2" t="n">
         <v>45683</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -745,15 +743,15 @@
       <c r="A24" s="5" t="n">
         <v>45693</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="2" t="n">
         <v>45704</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -761,15 +759,15 @@
       <c r="A26" s="5" t="n">
         <v>45779</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -777,7 +775,7 @@
       <c r="A28" s="5" t="n">
         <v>45840</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -785,7 +783,7 @@
       <c r="A29" s="5" t="n">
         <v>45841</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -793,61 +791,85 @@
       <c r="A30" s="5" t="n">
         <v>45845</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7"/>
-      <c r="B31" s="2" t="s">
+      <c r="A31" s="4"/>
+      <c r="B31" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="n">
+      <c r="A32" s="2" t="n">
         <v>45910</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="n">
+      <c r="A33" s="6" t="n">
         <v>45933</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8" t="n">
+      <c r="A35" s="6" t="n">
         <v>45943</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="n">
+      <c r="A36" s="6" t="n">
         <v>-501918</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="7" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/sueños.xlsx
+++ b/sueños.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
   <si>
     <t xml:space="preserve">* Con Malen discutimos antes de que entrara otra vez en ageac (el ritual de iniciacion)</t>
   </si>
@@ -170,6 +170,12 @@
   </si>
   <si>
     <t xml:space="preserve">x fiesta con genteextraña en diag 74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sanB doblexx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X jugando al futbol con ezequiel ibañez y mariano errazu</t>
   </si>
 </sst>
 </file>
@@ -551,7 +557,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="12.63"/>
@@ -870,6 +876,22 @@
       </c>
       <c r="B41" s="1" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/sueños.xlsx
+++ b/sueños.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
   <si>
     <t xml:space="preserve">* Con Malen discutimos antes de que entrara otra vez en ageac (el ritual de iniciacion)</t>
   </si>
@@ -176,6 +176,17 @@
   </si>
   <si>
     <t xml:space="preserve">X jugando al futbol con ezequiel ibañez y mariano errazu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x. vi en un frontispicio de un salon mi nombre interno, no lo recuerdo pero tambien se traducia a jonahtan la, chat gpt me dijo que le daba miedo decirme el significado, y me dio tres sinonimos de samael</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/marzo/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">malen no volvió a casa por tres dias, cuando llegó dijo que era porque habia tomado una pasti y las cosas se le fueron de las manos, terminamos.
+Sali a buscar alguna compoania por ahi.
+Andando en auto con mama, ella manejaba, ibamos por la arena, decide estacionar marcha atrás al corde de un precipicio, mientras veiamos caerse o andar rapido otros autos y gente morir, cuando quice salir vi que adelante habia un olectivo y no podia avanzar, la situacion era riezgosa, podia caer para atrás, a la derecha o encajar por ahi. Cero que decidi esperar que se valla el cole pero llamo la Ema</t>
   </si>
 </sst>
 </file>
@@ -274,7 +285,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -305,6 +316,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -557,7 +572,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="12.63"/>
@@ -892,6 +907,22 @@
       </c>
       <c r="B43" s="1" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
